--- a/mosip_master/xlsx/zone.xlsx
+++ b/mosip_master/xlsx/zone.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MOSIP\Mosip Codebase\Master-Data-Tool\mosip-data-sludi-1.3.0\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\SLUDI Offline Training\sludi-mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37D3651D-640A-45C9-9E79-44E0DF279B62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05A3A0BB-0C1E-442A-BFB3-E94DABB527E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,9 +16,9 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$A$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$A$61</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="19">
   <si>
     <t>lang_code</t>
   </si>
@@ -63,9 +63,6 @@
     <t>TRUE</t>
   </si>
   <si>
-    <t>Province</t>
-  </si>
-  <si>
     <t>tam</t>
   </si>
   <si>
@@ -75,15 +72,6 @@
     <t>Sri Lanka</t>
   </si>
   <si>
-    <t>01</t>
-  </si>
-  <si>
-    <t>Western</t>
-  </si>
-  <si>
-    <t>LKA/01</t>
-  </si>
-  <si>
     <t>sin</t>
   </si>
   <si>
@@ -91,18 +79,6 @@
   </si>
   <si>
     <t>நாடு</t>
-  </si>
-  <si>
-    <t>පළාත</t>
-  </si>
-  <si>
-    <t>மாகாணம்</t>
-  </si>
-  <si>
-    <t>බස්නාහිර</t>
-  </si>
-  <si>
-    <t>மேற்கு</t>
   </si>
   <si>
     <t>இலங்கை</t>
@@ -214,7 +190,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -239,9 +215,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -558,7 +531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H149"/>
+  <dimension ref="A1:H146"/>
   <sheetFormatPr defaultColWidth="8.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="17.88671875" customWidth="1"/>
@@ -600,10 +573,10 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
         <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>14</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -612,7 +585,7 @@
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>10</v>
@@ -620,25 +593,22 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3" t="s">
         <v>16</v>
       </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>11</v>
-      </c>
       <c r="F3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>10</v>
@@ -646,101 +616,35 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G5" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>10</v>
-      </c>
+    <row r="41" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E41"/>
+    </row>
+    <row r="42" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E42"/>
+    </row>
+    <row r="43" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E43"/>
     </row>
     <row r="44" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E44"/>
@@ -797,13 +701,13 @@
       <c r="E61"/>
     </row>
     <row r="62" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E62"/>
+      <c r="E62" s="8"/>
     </row>
     <row r="63" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E63"/>
+      <c r="E63" s="8"/>
     </row>
     <row r="64" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E64"/>
+      <c r="E64" s="8"/>
     </row>
     <row r="65" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E65" s="8"/>
@@ -986,13 +890,13 @@
       <c r="E124" s="8"/>
     </row>
     <row r="125" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E125" s="8"/>
+      <c r="E125"/>
     </row>
     <row r="126" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E126" s="8"/>
+      <c r="E126"/>
     </row>
     <row r="127" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E127" s="8"/>
+      <c r="E127"/>
     </row>
     <row r="128" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E128"/>
@@ -1049,19 +953,10 @@
       <c r="E145"/>
     </row>
     <row r="146" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E146"/>
-    </row>
-    <row r="147" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E147"/>
-    </row>
-    <row r="148" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E148"/>
-    </row>
-    <row r="149" spans="5:5" x14ac:dyDescent="0.3">
-      <c r="E149" s="7"/>
+      <c r="E146" s="7"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A64" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:A61" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
